--- a/캠핑준비.xlsx
+++ b/캠핑준비.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\01_Repo\01_doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2FA6BA-50F3-44FC-B701-4DDCBDF34832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08187976-EE13-439D-A755-39E4E16F4626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B35C64D8-44DB-4A7D-B642-3EC43ECC7117}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{B35C64D8-44DB-4A7D-B642-3EC43ECC7117}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="CheckList" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="114">
   <si>
     <t>육류</t>
   </si>
@@ -125,6 +126,345 @@
   </si>
   <si>
     <t>화로</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>텐트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구분</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>체크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>품목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>타프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그라운드 시트(or 방수포)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콜팩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>데크팩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팩망치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발포매트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>잠자리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자충매트(or 에어매트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기장판</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>릴선</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서큘레이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미니히터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(동계) 일산화탄소 감지기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>테이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쉘프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주방용품</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구이바다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코펠(or 냄비)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>키친타올</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수세미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냄비받침</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>그릇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수저</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>컵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>조미료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지퍼백</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비닐장갑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불멍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화로대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>방염장갑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안전&amp;위생</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상비약</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수건</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물티슈</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세면도구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분리수거 봉투</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>핸드폰 충전기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉장고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이스박스, 아이스팩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식재료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>워터저그(옵션)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>생수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>밀키트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이불, 침낭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>멀티탭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>랜턴(and 스탠드)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>충전케이블</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화장품</t>
+  </si>
+  <si>
+    <t>맥주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>와인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>석쇠</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>불쏘시개(집게)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>커피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쌀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전기밥솥(옵션)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쫄면/냉면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>마스크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>콩나물</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소금,후추(양념)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>육수알</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>식용유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>감자,고구마</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>칼, 도마, 가위, 집게</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>야채류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구이용 고기류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보조 랜턴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>토치(가스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>버너(가스)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모기향(킬러)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>후라이팬 or 그래들</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>모기퇴치기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>책</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -148,7 +488,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,6 +498,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -174,9 +520,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -490,6 +843,375 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55030995-16CE-4D22-A1D6-61227B46999E}">
+  <dimension ref="B3:P28"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="8.796875" style="2"/>
+    <col min="3" max="3" width="5.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.796875" style="2"/>
+    <col min="7" max="7" width="5.19921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.19921875" customWidth="1"/>
+    <col min="9" max="10" width="8.796875" customWidth="1"/>
+    <col min="11" max="11" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.59765625" customWidth="1"/>
+    <col min="14" max="14" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="5.19921875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.69921875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" t="s">
+        <v>87</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" t="s">
+        <v>88</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" t="s">
+        <v>89</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" t="s">
+        <v>76</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="P10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="H11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="B13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" t="s">
+        <v>25</v>
+      </c>
+      <c r="P15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" x14ac:dyDescent="0.4">
+      <c r="D16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" t="s">
+        <v>111</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D17" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="L17" t="s">
+        <v>101</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D21" t="s">
+        <v>44</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J23" t="s">
+        <v>64</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="D24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" t="s">
+        <v>60</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="H25" t="s">
+        <v>61</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="H26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="27" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="H27" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="4:16" x14ac:dyDescent="0.4">
+      <c r="H28" t="s">
+        <v>94</v>
+      </c>
+      <c r="L28" t="s">
+        <v>91</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD4F2274-69B8-43BC-839E-BF17B344F5BC}">
   <dimension ref="B3:R10"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
